--- a/TestData/Opencart_LoginData.xlsx
+++ b/TestData/Opencart_LoginData.xlsx
@@ -1,9 +1,9 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28827"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30131"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{269072BF-E61C-44A7-BA5C-3EFC9061C18C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{02382632-2747-457B-84FA-DDF1E010E579}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="11">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="10">
   <si>
     <t>username</t>
   </si>
@@ -37,9 +37,6 @@
     <t>res</t>
   </si>
   <si>
-    <t>pavanoltraining@gmail.com</t>
-  </si>
-  <si>
     <t>test123</t>
   </si>
   <si>
@@ -52,7 +49,7 @@
     <t>tesna1202@gmail.com</t>
   </si>
   <si>
-    <t>Tesna@1202</t>
+    <t>pavanol@gmail.com</t>
   </si>
 </sst>
 </file>
@@ -480,10 +477,10 @@
     </row>
     <row r="2" spans="1:3" ht="18.5" x14ac:dyDescent="0.45">
       <c r="A2" s="3" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>2</v>
@@ -491,10 +488,10 @@
     </row>
     <row r="3" spans="1:3" ht="18.5" x14ac:dyDescent="0.45">
       <c r="A3" s="3" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>3</v>
@@ -502,10 +499,10 @@
     </row>
     <row r="4" spans="1:3" ht="18.5" x14ac:dyDescent="0.45">
       <c r="A4" s="3" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>3</v>
@@ -513,10 +510,10 @@
     </row>
     <row r="5" spans="1:3" ht="18.5" x14ac:dyDescent="0.45">
       <c r="A5" s="3" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>3</v>
@@ -528,7 +525,7 @@
     <hyperlink ref="A4" r:id="rId2" xr:uid="{EB701B42-A320-4932-9568-F231C8F446AB}"/>
     <hyperlink ref="A3" r:id="rId3" xr:uid="{2C470B3A-2A6E-4E3F-904B-CF31F1A9D026}"/>
     <hyperlink ref="A5" r:id="rId4" xr:uid="{93910C2A-F79E-4AFA-A4B6-D7111D627E47}"/>
-    <hyperlink ref="B2" r:id="rId5" xr:uid="{F74250F7-AC94-4366-AE27-3CC944FC98BB}"/>
+    <hyperlink ref="B2" r:id="rId5" display="Tesna@1202" xr:uid="{F74250F7-AC94-4366-AE27-3CC944FC98BB}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId6"/>
